--- a/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
+++ b/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="СВОД 2 магазина" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Коротич — по месяцам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Крона — по месяцам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Коротич ДМ — по месяцам" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Крона ДМ — по месяцам" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ДМ скорректировано" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Коротич — по месяцам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Крона — по месяцам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Коротич ДМ — по месяцам" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Крона ДМ — по месяцам" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +60,12 @@
       <color rgb="00C00000"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +80,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -104,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,6 +132,11 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -749,157 +764,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Коротич — по месяцам</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ДЕДЫ МОРОЗЫ — СКОРРЕКТИРОВАННАЯ МАРЖА (с реальным себесом Кроны)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>В выгрузке у Кроны себес=0 → её маржа завышена. Здесь вычтен реальный себес Кроны (~292-314 ₽/шт по коду ДМ). Коротич — себес уже в выгрузке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Продажи шт</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Выручка к нам ₽</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Себестоимость ₽</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Логистика ₽</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Хранение ₽</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Реклама ₽</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>Комиссия ₽</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>Платн.приёмка ₽</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>Штрафы ₽</t>
-        </is>
-      </c>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>Брак ₽</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>Эквайринг ₽</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>Прочие ₽</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>Налог ₽</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>Маржа ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Сен 25</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>821</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>57916</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>4350</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>7748</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>21301</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>6100</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>48800</v>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Коротич ДМ: прод.шт</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Коротич ДМ маржа ₽</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Крона ДМ: прод.шт</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Крона маржа (выгрузка) ₽</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Крона себес реальный ₽</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Крона маржа СКОРР ₽</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО 2 магазина ДМ ₽</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -909,46 +840,25 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>17837</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>15013762</v>
+        <v>146</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>-63369</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6873386</v>
+        <v>15</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1614433</v>
+        <v>7197</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>4380</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1364616</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>5913760</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>2448</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>341452</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>1069860</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>1159062</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>2929039</v>
+        <v>2817</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-60552</v>
       </c>
     </row>
     <row r="6">
@@ -958,46 +868,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>26288</v>
+        <v>2423</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20610927</v>
+        <v>399429</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9599475</v>
+        <v>642</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2583792</v>
+        <v>421179</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0</v>
+        <v>188278</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2940391</v>
+        <v>232901</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>9955699</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>4794</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>462502</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>1575360</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>1532296</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>2377102</v>
+        <v>632330</v>
       </c>
     </row>
     <row r="7">
@@ -1007,46 +896,25 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>48231</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>36563533</v>
+        <v>19687</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-527872</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>16818074</v>
+        <v>6872</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>8226895</v>
+        <v>3236243</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>2022530</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>3575408</v>
+        <v>1213713</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>17618748</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>1158775</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>887696</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>2884140</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>2815863</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>1072372</v>
+        <v>685842</v>
       </c>
     </row>
     <row r="8">
@@ -1056,46 +924,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>31623</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>22035559</v>
+        <v>3256</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-632892</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>11462986</v>
+        <v>278</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3820235</v>
+        <v>43250</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>20458</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>2048323</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>10660518</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>498166</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>605191</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>1891500</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>1733920</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>558040</v>
+        <v>81836</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-38586</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-671477</v>
       </c>
     </row>
     <row r="9">
@@ -1105,46 +952,25 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>27254</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>20601226</v>
+        <v>166</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-27817</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>10554897</v>
+        <v>31</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2330318</v>
+        <v>6788</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>147495</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>2656259</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>10031358</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>410</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>641987</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>1634280</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>1574627</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>1696258</v>
+        <v>9074</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-2286</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-30103</v>
       </c>
     </row>
     <row r="10">
@@ -1154,95 +980,74 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>30638</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>28731523</v>
+        <v>55</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>-12380</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>14806729</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2934831</v>
+        <v>3128</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>187104</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1911573</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>13311854</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>11045</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>1017232</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>1837560</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>2138159</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>4908356</v>
+        <v>4088</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-960</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-13341</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>182692</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>143556530</v>
+        <v>25733</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>-864900</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>70173464</v>
+        <v>7852</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>21510591</v>
+        <v>3717785</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>359407</v>
+        <v>2310186</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>14504317</v>
+        <v>1407599</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>67513238</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>1675637</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>3956659</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>10892700</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>10960027</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>13589968</v>
+        <v>542699</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>ВЫВОД: по факту прошлого сезона Деды Морозы (2 магазина) дали ≈ 542,699 ₽ чистой маржи — почти в ноль.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Коротич ДМ в убытке; Крона в плюсе только без учёта себеса. Главная причина — логистика (ДМ объёмные) + возвраты после НГ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Следствие для плана: не рассчитывать на 350 ₽/шт прибыли. Снижать логистику (локализация складов), минимизировать возвраты, точнее цена под сезон.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1279,7 +1084,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Крона — по месяцам</t>
+          <t>Коротич — по месяцам</t>
         </is>
       </c>
     </row>
@@ -1367,25 +1172,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>57916</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>4350</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>7748</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>21301</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -1397,16 +1202,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="5">
@@ -1416,46 +1221,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>15</v>
+        <v>17837</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16436</v>
+        <v>15013762</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>6873386</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4730</v>
+        <v>1614433</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>1364616</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>5289</v>
+        <v>5913760</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3467</v>
+        <v>2448</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>275</v>
+        <v>341452</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>900</v>
+        <v>1069860</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>141</v>
+        <v>1159062</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>7197</v>
+        <v>2929039</v>
       </c>
     </row>
     <row r="6">
@@ -1465,46 +1270,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>642</v>
+        <v>26288</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>643544</v>
+        <v>20610927</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>9599475</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>177094</v>
+        <v>2583792</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>2940391</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>139773</v>
+        <v>9955699</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1831</v>
+        <v>4794</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>11805</v>
+        <v>462502</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>38400</v>
+        <v>1575360</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>5168</v>
+        <v>1532296</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>421179</v>
+        <v>2377102</v>
       </c>
     </row>
     <row r="7">
@@ -1514,46 +1319,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6886</v>
+        <v>48231</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>6002296</v>
+        <v>36563533</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>16818074</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2101307</v>
+        <v>8226895</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2592</v>
+        <v>3575408</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1369174</v>
+        <v>17618748</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>197663</v>
+        <v>1158775</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>133756</v>
+        <v>887696</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>409860</v>
+        <v>2884140</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>50109</v>
+        <v>2815863</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>3241785</v>
+        <v>1072372</v>
       </c>
     </row>
     <row r="8">
@@ -1563,46 +1368,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>350</v>
+        <v>31623</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>244080</v>
+        <v>22035559</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>11462986</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>127982</v>
+        <v>3820235</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>6</v>
+        <v>20458</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>426</v>
+        <v>2048323</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>53912</v>
+        <v>10660518</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3196</v>
+        <v>498166</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5808</v>
+        <v>605191</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>20580</v>
+        <v>1891500</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>11547</v>
+        <v>1733920</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>79019</v>
+        <v>558040</v>
       </c>
     </row>
     <row r="9">
@@ -1612,46 +1417,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>205</v>
+        <v>27254</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>151471</v>
+        <v>20601226</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>10554897</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>29260</v>
+        <v>2330318</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>184</v>
+        <v>147495</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1</v>
+        <v>2656259</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>33030</v>
+        <v>10031358</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3912</v>
+        <v>641987</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>12300</v>
+        <v>1634280</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>7228</v>
+        <v>1574627</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>97705</v>
+        <v>1696258</v>
       </c>
     </row>
     <row r="10">
@@ -1661,46 +1466,46 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>66</v>
+        <v>30638</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>58271</v>
+        <v>28731523</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>14806729</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>10951</v>
+        <v>2934831</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>361</v>
+        <v>187104</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>1911573</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>15073</v>
+        <v>13311854</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>11045</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1873</v>
+        <v>1017232</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3960</v>
+        <v>1837560</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2749</v>
+        <v>2138159</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>40971</v>
+        <v>4908356</v>
       </c>
     </row>
     <row r="11">
@@ -1710,46 +1515,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>8164</v>
+        <v>182692</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>7116097</v>
+        <v>143556530</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>70173464</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>2451322</v>
+        <v>21510591</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>551</v>
+        <v>359407</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>3018</v>
+        <v>14504317</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1616252</v>
+        <v>67513238</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>206157</v>
+        <v>1675637</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>157430</v>
+        <v>3956659</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>486000</v>
+        <v>10892700</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>76942</v>
+        <v>10960027</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>3887857</v>
+        <v>13589968</v>
       </c>
     </row>
   </sheetData>
@@ -1784,9 +1589,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Коротич ДМ — по месяцам</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Крона — по месяцам</t>
         </is>
       </c>
     </row>
@@ -1874,25 +1679,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -1904,16 +1709,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1923,46 +1728,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>171695</v>
+        <v>16436</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>42775</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54864</v>
+        <v>4730</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>117937</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>61041</v>
+        <v>5289</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>3467</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3210</v>
+        <v>275</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>8640</v>
+        <v>900</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>11741</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>-63369</v>
+        <v>141</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>7197</v>
       </c>
     </row>
     <row r="6">
@@ -1972,46 +1777,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2423</v>
+        <v>642</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2984257</v>
+        <v>643544</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>740850</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>751861</v>
+        <v>177094</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>743282</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1322609</v>
+        <v>139773</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>1831</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53386</v>
+        <v>11805</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>143820</v>
+        <v>38400</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>206248</v>
+        <v>5168</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>399429</v>
+        <v>421179</v>
       </c>
     </row>
     <row r="7">
@@ -2021,46 +1826,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>19687</v>
+        <v>6886</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>14509692</v>
+        <v>6002296</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6022535</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5818639</v>
+        <v>2101307</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>930646</v>
+        <v>2592</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>6535961</v>
+        <v>1369174</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>11016</v>
+        <v>197663</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>360235</v>
+        <v>133756</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1172100</v>
+        <v>409860</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>1086862</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>-527872</v>
+        <v>50109</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>3241785</v>
       </c>
     </row>
     <row r="8">
@@ -2070,46 +1875,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3256</v>
+        <v>350</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1920705</v>
+        <v>244080</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>999941</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1215186</v>
+        <v>127982</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>840845</v>
+        <v>53912</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>4248</v>
+        <v>3196</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>51642</v>
+        <v>5808</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>191280</v>
+        <v>20580</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>139539</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>-632892</v>
+        <v>11547</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>79019</v>
       </c>
     </row>
     <row r="9">
@@ -2119,46 +1924,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>109201</v>
+        <v>151471</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53533</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>60309</v>
+        <v>29260</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>37361</v>
+        <v>33030</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2608</v>
+        <v>3912</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>9720</v>
+        <v>12300</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>6576</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>-27817</v>
+        <v>7228</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>97705</v>
       </c>
     </row>
     <row r="10">
@@ -2168,25 +1973,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>38352</v>
+        <v>58271</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>17210</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>20468</v>
+        <v>10951</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>72</v>
+        <v>361</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6269</v>
+        <v>15073</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
@@ -2198,16 +2003,16 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1159</v>
+        <v>1873</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2397</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>-12380</v>
+        <v>2749</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>40971</v>
       </c>
     </row>
     <row r="11">
@@ -2217,46 +2022,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>25737</v>
+        <v>8164</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>19733900</v>
+        <v>7116097</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>7877428</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>7921330</v>
+        <v>2451322</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>259</v>
+        <v>551</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>1792382</v>
+        <v>3018</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>8806181</v>
+        <v>1616252</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>15354</v>
+        <v>206157</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>472253</v>
+        <v>157430</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>1528860</v>
+        <v>486000</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>1453403</v>
+        <v>76942</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>-864587</v>
+        <v>3887857</v>
       </c>
     </row>
   </sheetData>
@@ -2293,6 +2098,513 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
+          <t>Коротич ДМ — по месяцам</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Платн.приёмка ₽</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Брак ₽</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Сен 25</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>584</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2095</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Окт 25</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>171695</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>42775</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>54864</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>117937</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>61041</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>3210</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>8640</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>11741</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>-63369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ноя 25</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2423</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2984257</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>740850</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>751861</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>743282</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1322609</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>53386</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>143820</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>206248</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>399429</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Дек 25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>19687</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>14509692</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6022535</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5818639</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>930646</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>6535961</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>11016</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>360235</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1172100</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1086862</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>-527872</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Янв 26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3256</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1920705</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>999941</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1215186</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>840845</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>4248</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>51642</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>191280</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>139539</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>-632892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Фев 26</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>109201</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>53533</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>60309</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>37361</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2608</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9720</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>6576</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>-27817</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Мар 26</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>38352</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>17210</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>20468</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6269</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1159</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2397</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>-12380</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>25737</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>19733900</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>7877428</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>7921330</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>259</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>1792382</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>8806181</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>15354</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>472253</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>1528860</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>1453403</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>-864587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
           <t>Крона ДМ — по месяцам</t>
         </is>
       </c>

--- a/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
+++ b/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
@@ -65,7 +65,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +85,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -114,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,6 +147,12 @@
     </xf>
     <xf numFmtId="3" fontId="8" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -652,37 +668,37 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Крона — ВСЁ</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  в т.ч. Деды Морозы (себес Кроны учтён)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
         <v>7116097</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="C7" s="17" t="n">
+        <v>2310186</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <v>2451322</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="17" t="n">
         <v>551</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="17" t="n">
         <v>3018</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="17" t="n">
         <v>1616252</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="17" t="n">
         <v>849587</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="17" t="n">
         <v>76942</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>3887857</v>
+      <c r="J7" s="18" t="n">
+        <v>1407599</v>
       </c>
     </row>
     <row r="8">
@@ -751,6 +767,68 @@
       </c>
       <c r="J9" s="8" t="n">
         <v>17477825</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>ДЕДЫ МОРОЗЫ 2 магазина (скорр.)</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>26614245</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>10187614</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>10339751</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>344</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>1792382</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>10360001</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>2840967</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>1519014</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>543012</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Примечания:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>• У Кроны в выгрузке себестоимость = 0. По Дедам Морозам себес Кроны восстановлен (~292-314 ₽/шт по коду) и вычтен — строка 7 и итог ДМ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>• Честная маржа Дедов Морозов за сезон окт-мар (2 магазина) = ~543 тыс ₽ (почти ноль). Коротич ДМ в убытке, Крона в плюсе; вся прибыль — ноя-дек, январь-март съедают возвраты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>• Маржа «Крона — ВСЁ» (строка 6) по не-ДМ товарам осталась без себеса (его нет в выгрузке) — фактически тоже завышена.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
+++ b/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="СВОД 2 магазина" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ДМ скорректировано" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Коротич — по месяцам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Крона — по месяцам" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Коротич ДМ — по месяцам" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Крона ДМ — по месяцам" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Я-Ф-М 2026 по магазинам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ДМ скорректировано" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Коротич — по месяцам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Крона — по месяцам" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Коротич ДМ — по месяцам" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Крона ДМ — по месяцам" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +154,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -842,6 +845,478 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>РАСХОДЫ ПО МАГАЗИНАМ — ЯНВАРЬ / ФЕВРАЛЬ / МАРТ 2026 (WB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Коротич Янв</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Коротич Фев</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Коротич Мар</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Крона Янв</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Крона Фев</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Крона Мар</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>ИТОГО 2 маг</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>31623</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>27254</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>30638</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>90136</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>22035559</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>20601226</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>28731523</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>244080</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>151471</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>58271</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>71822130</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>11462986</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10554897</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>14806729</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>36824612</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10660518</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>10031358</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>13311854</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>53912</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>33030</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>15073</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>34105745</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3820235</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2330318</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2934831</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>127982</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>29260</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>10951</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>9253576</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>20458</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>147495</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>187104</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>361</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>355608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>2048323</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2656259</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1911573</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>426</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6616582</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Платн.приёмка ₽</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>498166</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>410</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11045</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3196</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>512816</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Брак ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>605191</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>641987</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1017232</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5808</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>3912</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1873</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>2276003</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1891500</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1634280</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1837560</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>20580</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>3960</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>5400180</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1733920</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1574627</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2138159</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>11547</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>7228</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2749</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5468231</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>558040</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>1696258</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>4908356</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>79019</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>97705</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>40971</v>
+      </c>
+      <c r="H17" s="23" t="n">
+        <v>7380351</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Примечание: у Кроны себестоимость в выгрузке = 0, поэтому её «Себестоимость» и «Маржа» завышены.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1126,513 +1601,6 @@
         <is>
           <t>Следствие для плана: не рассчитывать на 350 ₽/шт прибыли. Снижать логистику (локализация складов), минимизировать возвраты, точнее цена под сезон.</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Коротич — по месяцам</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Продажи шт</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Выручка к нам ₽</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Себестоимость ₽</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Логистика ₽</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Хранение ₽</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Реклама ₽</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>Комиссия ₽</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>Платн.приёмка ₽</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>Штрафы ₽</t>
-        </is>
-      </c>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>Брак ₽</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>Эквайринг ₽</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>Прочие ₽</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>Налог ₽</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>Маржа ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Сен 25</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>821</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>57916</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>4350</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>7748</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>21301</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>6100</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>48800</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Окт 25</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>17837</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>15013762</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>6873386</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1614433</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>1364616</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>5913760</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>2448</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>341452</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>1069860</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>1159062</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>2929039</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Ноя 25</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>26288</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>20610927</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>9599475</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2583792</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>2940391</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>9955699</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>4794</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>462502</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>1575360</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>1532296</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>2377102</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Дек 25</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>48231</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>36563533</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>16818074</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>8226895</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>3575408</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>17618748</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>1158775</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>887696</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>2884140</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>2815863</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>1072372</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Янв 26</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>31623</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>22035559</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>11462986</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>3820235</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>20458</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>2048323</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>10660518</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>498166</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>605191</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>1891500</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>1733920</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>558040</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Фев 26</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>27254</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>20601226</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>10554897</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>2330318</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>147495</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>2656259</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>10031358</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>410</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>641987</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>1634280</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>1574627</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>1696258</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Мар 26</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>30638</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>28731523</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>14806729</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2934831</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>187104</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1911573</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>13311854</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>11045</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>1017232</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>1837560</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>2138159</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>4908356</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>182692</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>143556530</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>70173464</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>21510591</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>359407</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>14504317</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>67513238</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>1675637</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>3956659</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>10892700</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>10960027</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>13589968</v>
       </c>
     </row>
   </sheetData>
@@ -1669,7 +1637,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Крона — по месяцам</t>
+          <t>Коротич — по месяцам</t>
         </is>
       </c>
     </row>
@@ -1757,25 +1725,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>57916</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>4350</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>7748</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>21301</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -1787,16 +1755,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="5">
@@ -1806,46 +1774,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>15</v>
+        <v>17837</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16436</v>
+        <v>15013762</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>6873386</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4730</v>
+        <v>1614433</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>1364616</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>5289</v>
+        <v>5913760</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3467</v>
+        <v>2448</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>275</v>
+        <v>341452</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>900</v>
+        <v>1069860</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>141</v>
+        <v>1159062</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>7197</v>
+        <v>2929039</v>
       </c>
     </row>
     <row r="6">
@@ -1855,46 +1823,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>642</v>
+        <v>26288</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>643544</v>
+        <v>20610927</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>9599475</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>177094</v>
+        <v>2583792</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>2940391</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>139773</v>
+        <v>9955699</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1831</v>
+        <v>4794</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>11805</v>
+        <v>462502</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>38400</v>
+        <v>1575360</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>5168</v>
+        <v>1532296</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>421179</v>
+        <v>2377102</v>
       </c>
     </row>
     <row r="7">
@@ -1904,46 +1872,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6886</v>
+        <v>48231</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>6002296</v>
+        <v>36563533</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>16818074</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2101307</v>
+        <v>8226895</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2592</v>
+        <v>3575408</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1369174</v>
+        <v>17618748</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>197663</v>
+        <v>1158775</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>133756</v>
+        <v>887696</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>409860</v>
+        <v>2884140</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>50109</v>
+        <v>2815863</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>3241785</v>
+        <v>1072372</v>
       </c>
     </row>
     <row r="8">
@@ -1953,46 +1921,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>350</v>
+        <v>31623</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>244080</v>
+        <v>22035559</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>11462986</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>127982</v>
+        <v>3820235</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>6</v>
+        <v>20458</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>426</v>
+        <v>2048323</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>53912</v>
+        <v>10660518</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3196</v>
+        <v>498166</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5808</v>
+        <v>605191</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>20580</v>
+        <v>1891500</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>11547</v>
+        <v>1733920</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>79019</v>
+        <v>558040</v>
       </c>
     </row>
     <row r="9">
@@ -2002,46 +1970,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>205</v>
+        <v>27254</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>151471</v>
+        <v>20601226</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>10554897</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>29260</v>
+        <v>2330318</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>184</v>
+        <v>147495</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1</v>
+        <v>2656259</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>33030</v>
+        <v>10031358</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3912</v>
+        <v>641987</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>12300</v>
+        <v>1634280</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>7228</v>
+        <v>1574627</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>97705</v>
+        <v>1696258</v>
       </c>
     </row>
     <row r="10">
@@ -2051,46 +2019,46 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>66</v>
+        <v>30638</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>58271</v>
+        <v>28731523</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>14806729</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>10951</v>
+        <v>2934831</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>361</v>
+        <v>187104</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>1911573</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>15073</v>
+        <v>13311854</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>11045</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1873</v>
+        <v>1017232</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3960</v>
+        <v>1837560</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2749</v>
+        <v>2138159</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>40971</v>
+        <v>4908356</v>
       </c>
     </row>
     <row r="11">
@@ -2100,46 +2068,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>8164</v>
+        <v>182692</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>7116097</v>
+        <v>143556530</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>70173464</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>2451322</v>
+        <v>21510591</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>551</v>
+        <v>359407</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>3018</v>
+        <v>14504317</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1616252</v>
+        <v>67513238</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>206157</v>
+        <v>1675637</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>157430</v>
+        <v>3956659</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>486000</v>
+        <v>10892700</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>76942</v>
+        <v>10960027</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>3887857</v>
+        <v>13589968</v>
       </c>
     </row>
   </sheetData>
@@ -2174,9 +2142,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Коротич ДМ — по месяцам</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Крона — по месяцам</t>
         </is>
       </c>
     </row>
@@ -2264,25 +2232,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -2294,16 +2262,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2313,46 +2281,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>171695</v>
+        <v>16436</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>42775</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54864</v>
+        <v>4730</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>117937</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>61041</v>
+        <v>5289</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>3467</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3210</v>
+        <v>275</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>8640</v>
+        <v>900</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>11741</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>-63369</v>
+        <v>141</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>7197</v>
       </c>
     </row>
     <row r="6">
@@ -2362,46 +2330,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2423</v>
+        <v>642</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2984257</v>
+        <v>643544</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>740850</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>751861</v>
+        <v>177094</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>743282</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1322609</v>
+        <v>139773</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>1831</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53386</v>
+        <v>11805</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>143820</v>
+        <v>38400</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>206248</v>
+        <v>5168</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>399429</v>
+        <v>421179</v>
       </c>
     </row>
     <row r="7">
@@ -2411,46 +2379,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>19687</v>
+        <v>6886</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>14509692</v>
+        <v>6002296</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6022535</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5818639</v>
+        <v>2101307</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>930646</v>
+        <v>2592</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>6535961</v>
+        <v>1369174</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>11016</v>
+        <v>197663</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>360235</v>
+        <v>133756</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1172100</v>
+        <v>409860</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>1086862</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>-527872</v>
+        <v>50109</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>3241785</v>
       </c>
     </row>
     <row r="8">
@@ -2460,46 +2428,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3256</v>
+        <v>350</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1920705</v>
+        <v>244080</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>999941</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1215186</v>
+        <v>127982</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>840845</v>
+        <v>53912</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>4248</v>
+        <v>3196</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>51642</v>
+        <v>5808</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>191280</v>
+        <v>20580</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>139539</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>-632892</v>
+        <v>11547</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>79019</v>
       </c>
     </row>
     <row r="9">
@@ -2509,46 +2477,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>109201</v>
+        <v>151471</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53533</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>60309</v>
+        <v>29260</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>37361</v>
+        <v>33030</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2608</v>
+        <v>3912</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>9720</v>
+        <v>12300</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>6576</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>-27817</v>
+        <v>7228</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>97705</v>
       </c>
     </row>
     <row r="10">
@@ -2558,25 +2526,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>38352</v>
+        <v>58271</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>17210</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>20468</v>
+        <v>10951</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>72</v>
+        <v>361</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6269</v>
+        <v>15073</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
@@ -2588,16 +2556,16 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1159</v>
+        <v>1873</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2397</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>-12380</v>
+        <v>2749</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>40971</v>
       </c>
     </row>
     <row r="11">
@@ -2607,46 +2575,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>25737</v>
+        <v>8164</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>19733900</v>
+        <v>7116097</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>7877428</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>7921330</v>
+        <v>2451322</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>259</v>
+        <v>551</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>1792382</v>
+        <v>3018</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>8806181</v>
+        <v>1616252</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>15354</v>
+        <v>206157</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>472253</v>
+        <v>157430</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>1528860</v>
+        <v>486000</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>1453403</v>
+        <v>76942</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>-864587</v>
+        <v>3887857</v>
       </c>
     </row>
   </sheetData>
@@ -2683,6 +2651,513 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
+          <t>Коротич ДМ — по месяцам</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Платн.приёмка ₽</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Брак ₽</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Сен 25</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>584</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2095</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Окт 25</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>171695</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>42775</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>54864</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>117937</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>61041</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>3210</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>8640</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>11741</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>-63369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ноя 25</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2423</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2984257</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>740850</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>751861</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>743282</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1322609</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>53386</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>143820</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>206248</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>399429</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Дек 25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>19687</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>14509692</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6022535</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5818639</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>930646</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>6535961</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>11016</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>360235</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1172100</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1086862</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>-527872</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Янв 26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3256</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1920705</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>999941</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1215186</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>840845</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>4248</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>51642</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>191280</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>139539</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>-632892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Фев 26</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>109201</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>53533</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>60309</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>37361</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2608</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9720</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>6576</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>-27817</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Мар 26</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>38352</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>17210</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>20468</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6269</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1159</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2397</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>-12380</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>25737</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>19733900</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>7877428</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>7921330</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>259</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>1792382</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>8806181</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>15354</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>472253</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>1528860</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>1453403</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>-864587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
           <t>Крона ДМ — по месяцам</t>
         </is>
       </c>

--- a/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
+++ b/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="СВОД 2 магазина" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Я-Ф-М 2026 по магазинам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ДМ скорректировано" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Коротич — по месяцам" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Крона — по месяцам" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Коротич ДМ — по месяцам" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Крона ДМ — по месяцам" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ДМ Я-Ф-М 2026 по магазинам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Я-Ф-М 2026 по магазинам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ДМ скорректировано" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Коротич — по месяцам" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Крона — по месяцам" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Коротич ДМ — по месяцам" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Крона ДМ — по месяцам" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +65,11 @@
     <font>
       <b val="1"/>
       <color rgb="00C00000"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +162,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -848,6 +855,465 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ДЕДЫ МОРОЗЫ — РАСХОДЫ ПО МАГАЗИНАМ, ЯНВ-ФЕВ-МАР 2026 (что съело прибыль)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Период после НГ: продаж почти нет, а расходы идут (возвраты, логистика). У Кроны себес восстановлен (~300 ₽/шт).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Коротич Янв</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Коротич Фев</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Коротич Мар</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Крона Янв</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Крона Фев</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Крона Мар</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3256</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Возвраты шт</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1920705</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>109201</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>38352</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>193682</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>25421</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9232</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2296593</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>999941</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>53533</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>17210</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>83820</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9314</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>4200</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1168018</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>840845</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>37361</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>6269</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>40621</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-357</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>926760</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1215186</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>60309</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>20468</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>120686</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>11037</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>4768</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1432454</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4248</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3196</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7534</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>51642</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2608</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1159</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>4663</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>60845</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>191280</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>9720</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>16260</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>223260</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>139539</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6576</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2397</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8961</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>887</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>438</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>158798</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>-632892</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>-27817</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>-12380</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>-40570</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>-2526</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>-1072</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>-717257</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГ ДМ за янв-мар 2026: продажи 3,800 шт, ВОЗВРАТЫ 79 шт, логистика 1,432,454 ₽, МАРЖА -717,257 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>ГЛАВНОЕ: прибыль съела ЛОГИСТИКА — Деды Морозы объёмные, логистика ~370 ₽/шт. За янв-мар 1,43 млн ₽ логистики против слабых послепраздничных продаж. Возвратов мало (79 шт), дело не в них.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
@@ -1311,7 +1777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1601,513 +2067,6 @@
         <is>
           <t>Следствие для плана: не рассчитывать на 350 ₽/шт прибыли. Снижать логистику (локализация складов), минимизировать возвраты, точнее цена под сезон.</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Коротич — по месяцам</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Продажи шт</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Выручка к нам ₽</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Себестоимость ₽</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Логистика ₽</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Хранение ₽</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Реклама ₽</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>Комиссия ₽</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>Платн.приёмка ₽</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>Штрафы ₽</t>
-        </is>
-      </c>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>Брак ₽</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>Эквайринг ₽</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>Прочие ₽</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>Налог ₽</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>Маржа ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Сен 25</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>821</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>57916</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>4350</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>7748</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>21301</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>6100</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>48800</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Окт 25</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>17837</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>15013762</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>6873386</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1614433</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>1364616</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>5913760</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>2448</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>341452</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>1069860</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>1159062</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>2929039</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Ноя 25</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>26288</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>20610927</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>9599475</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2583792</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>2940391</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>9955699</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>4794</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>462502</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>1575360</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>1532296</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>2377102</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Дек 25</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>48231</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>36563533</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>16818074</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>8226895</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>3575408</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>17618748</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>1158775</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>887696</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>2884140</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>2815863</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>1072372</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Янв 26</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>31623</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>22035559</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>11462986</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>3820235</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>20458</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>2048323</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>10660518</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>498166</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>605191</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>1891500</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>1733920</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>558040</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Фев 26</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>27254</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>20601226</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>10554897</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>2330318</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>147495</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>2656259</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>10031358</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>410</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>641987</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>1634280</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>1574627</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>1696258</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Мар 26</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>30638</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>28731523</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>14806729</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2934831</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>187104</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1911573</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>13311854</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>11045</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>1017232</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>1837560</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>2138159</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>4908356</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>182692</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>143556530</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>70173464</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>21510591</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>359407</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>14504317</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>67513238</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>1675637</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>3956659</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>10892700</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>10960027</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>13589968</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +2103,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Крона — по месяцам</t>
+          <t>Коротич — по месяцам</t>
         </is>
       </c>
     </row>
@@ -2232,25 +2191,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>57916</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>4350</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>7748</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>21301</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -2262,16 +2221,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="5">
@@ -2281,46 +2240,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>15</v>
+        <v>17837</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16436</v>
+        <v>15013762</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>6873386</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4730</v>
+        <v>1614433</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>1364616</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>5289</v>
+        <v>5913760</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3467</v>
+        <v>2448</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>275</v>
+        <v>341452</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>900</v>
+        <v>1069860</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>141</v>
+        <v>1159062</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>7197</v>
+        <v>2929039</v>
       </c>
     </row>
     <row r="6">
@@ -2330,46 +2289,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>642</v>
+        <v>26288</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>643544</v>
+        <v>20610927</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>9599475</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>177094</v>
+        <v>2583792</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>2940391</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>139773</v>
+        <v>9955699</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1831</v>
+        <v>4794</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>11805</v>
+        <v>462502</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>38400</v>
+        <v>1575360</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>5168</v>
+        <v>1532296</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>421179</v>
+        <v>2377102</v>
       </c>
     </row>
     <row r="7">
@@ -2379,46 +2338,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6886</v>
+        <v>48231</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>6002296</v>
+        <v>36563533</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>16818074</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2101307</v>
+        <v>8226895</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2592</v>
+        <v>3575408</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1369174</v>
+        <v>17618748</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>197663</v>
+        <v>1158775</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>133756</v>
+        <v>887696</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>409860</v>
+        <v>2884140</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>50109</v>
+        <v>2815863</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>3241785</v>
+        <v>1072372</v>
       </c>
     </row>
     <row r="8">
@@ -2428,46 +2387,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>350</v>
+        <v>31623</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>244080</v>
+        <v>22035559</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>11462986</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>127982</v>
+        <v>3820235</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>6</v>
+        <v>20458</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>426</v>
+        <v>2048323</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>53912</v>
+        <v>10660518</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3196</v>
+        <v>498166</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5808</v>
+        <v>605191</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>20580</v>
+        <v>1891500</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>11547</v>
+        <v>1733920</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>79019</v>
+        <v>558040</v>
       </c>
     </row>
     <row r="9">
@@ -2477,46 +2436,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>205</v>
+        <v>27254</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>151471</v>
+        <v>20601226</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>10554897</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>29260</v>
+        <v>2330318</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>184</v>
+        <v>147495</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1</v>
+        <v>2656259</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>33030</v>
+        <v>10031358</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3912</v>
+        <v>641987</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>12300</v>
+        <v>1634280</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>7228</v>
+        <v>1574627</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>97705</v>
+        <v>1696258</v>
       </c>
     </row>
     <row r="10">
@@ -2526,46 +2485,46 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>66</v>
+        <v>30638</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>58271</v>
+        <v>28731523</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>14806729</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>10951</v>
+        <v>2934831</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>361</v>
+        <v>187104</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>1911573</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>15073</v>
+        <v>13311854</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>11045</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1873</v>
+        <v>1017232</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3960</v>
+        <v>1837560</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2749</v>
+        <v>2138159</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>40971</v>
+        <v>4908356</v>
       </c>
     </row>
     <row r="11">
@@ -2575,46 +2534,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>8164</v>
+        <v>182692</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>7116097</v>
+        <v>143556530</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>70173464</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>2451322</v>
+        <v>21510591</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>551</v>
+        <v>359407</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>3018</v>
+        <v>14504317</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1616252</v>
+        <v>67513238</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>206157</v>
+        <v>1675637</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>157430</v>
+        <v>3956659</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>486000</v>
+        <v>10892700</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>76942</v>
+        <v>10960027</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>3887857</v>
+        <v>13589968</v>
       </c>
     </row>
   </sheetData>
@@ -2649,9 +2608,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Коротич ДМ — по месяцам</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Крона — по месяцам</t>
         </is>
       </c>
     </row>
@@ -2739,25 +2698,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -2769,16 +2728,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2788,46 +2747,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>171695</v>
+        <v>16436</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>42775</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54864</v>
+        <v>4730</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>117937</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>61041</v>
+        <v>5289</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>3467</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3210</v>
+        <v>275</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>8640</v>
+        <v>900</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>11741</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>-63369</v>
+        <v>141</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>7197</v>
       </c>
     </row>
     <row r="6">
@@ -2837,46 +2796,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2423</v>
+        <v>642</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2984257</v>
+        <v>643544</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>740850</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>751861</v>
+        <v>177094</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>743282</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1322609</v>
+        <v>139773</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>1831</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53386</v>
+        <v>11805</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>143820</v>
+        <v>38400</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>206248</v>
+        <v>5168</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>399429</v>
+        <v>421179</v>
       </c>
     </row>
     <row r="7">
@@ -2886,46 +2845,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>19687</v>
+        <v>6886</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>14509692</v>
+        <v>6002296</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6022535</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5818639</v>
+        <v>2101307</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>930646</v>
+        <v>2592</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>6535961</v>
+        <v>1369174</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>11016</v>
+        <v>197663</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>360235</v>
+        <v>133756</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1172100</v>
+        <v>409860</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>1086862</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>-527872</v>
+        <v>50109</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>3241785</v>
       </c>
     </row>
     <row r="8">
@@ -2935,46 +2894,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3256</v>
+        <v>350</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1920705</v>
+        <v>244080</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>999941</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1215186</v>
+        <v>127982</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>840845</v>
+        <v>53912</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>4248</v>
+        <v>3196</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>51642</v>
+        <v>5808</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>191280</v>
+        <v>20580</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>139539</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>-632892</v>
+        <v>11547</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>79019</v>
       </c>
     </row>
     <row r="9">
@@ -2984,46 +2943,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>109201</v>
+        <v>151471</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53533</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>60309</v>
+        <v>29260</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>37361</v>
+        <v>33030</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2608</v>
+        <v>3912</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>9720</v>
+        <v>12300</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>6576</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>-27817</v>
+        <v>7228</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>97705</v>
       </c>
     </row>
     <row r="10">
@@ -3033,25 +2992,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>38352</v>
+        <v>58271</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>17210</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>20468</v>
+        <v>10951</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>72</v>
+        <v>361</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6269</v>
+        <v>15073</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
@@ -3063,16 +3022,16 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1159</v>
+        <v>1873</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2397</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>-12380</v>
+        <v>2749</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>40971</v>
       </c>
     </row>
     <row r="11">
@@ -3082,46 +3041,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>25737</v>
+        <v>8164</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>19733900</v>
+        <v>7116097</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>7877428</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>7921330</v>
+        <v>2451322</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>259</v>
+        <v>551</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>1792382</v>
+        <v>3018</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>8806181</v>
+        <v>1616252</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>15354</v>
+        <v>206157</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>472253</v>
+        <v>157430</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>1528860</v>
+        <v>486000</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>1453403</v>
+        <v>76942</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>-864587</v>
+        <v>3887857</v>
       </c>
     </row>
   </sheetData>
@@ -3158,6 +3117,513 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
+          <t>Коротич ДМ — по месяцам</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Платн.приёмка ₽</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Брак ₽</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Сен 25</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>584</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2095</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Окт 25</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>171695</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>42775</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>54864</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>117937</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>61041</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>3210</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>8640</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>11741</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>-63369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ноя 25</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2423</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2984257</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>740850</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>751861</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>743282</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1322609</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>53386</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>143820</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>206248</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>399429</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Дек 25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>19687</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>14509692</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6022535</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5818639</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>930646</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>6535961</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>11016</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>360235</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1172100</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1086862</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>-527872</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Янв 26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3256</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1920705</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>999941</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1215186</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>840845</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>4248</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>51642</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>191280</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>139539</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>-632892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Фев 26</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>109201</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>53533</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>60309</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>37361</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2608</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9720</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>6576</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>-27817</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Мар 26</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>38352</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>17210</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>20468</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6269</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1159</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2397</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>-12380</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>25737</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>19733900</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>7877428</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>7921330</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>259</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>1792382</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>8806181</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>15354</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>472253</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>1528860</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>1453403</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>-864587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
           <t>Крона ДМ — по месяцам</t>
         </is>
       </c>

--- a/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
+++ b/outputs/plan/затраты_2_магазина_по_месяцам.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="СВОД 2 магазина" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ДМ Я-Ф-М 2026 по магазинам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Я-Ф-М 2026 по магазинам" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ДМ скорректировано" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Коротич — по месяцам" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Крона — по месяцам" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Коротич ДМ — по месяцам" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Крона ДМ — по месяцам" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ДМ полная картина" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ДМ Я-Ф-М 2026 по магазинам" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Я-Ф-М 2026 по магазинам" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ДМ скорректировано" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Коротич — по месяцам" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Крона — по месяцам" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Коротич ДМ — по месяцам" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Крона ДМ — по месяцам" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +72,13 @@
       <color rgb="00C00000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +110,31 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +194,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -852,6 +898,1367 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>ДЕДЫ МОРОЗЫ — ПОЛНАЯ КАРТИНА ПО ДВУМ МАГАЗИНАМ (сен-2025 … мар-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Себес Кроны восстановлен (~300 ₽/шт). Маржа — скорректированная. Видно по каждому магазину и месяцу все расходы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Сен 25</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Окт 25</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Ноя 25</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Дек 25</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Янв 26</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>Фев 26</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>Мар 26</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>КОРОТИЧ — Деды Морозы</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
+      <c r="H5" s="27" t="n"/>
+      <c r="I5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>146</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>2423</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>19687</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>3256</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>166</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>55</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>25737</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Возвраты шт</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>26</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>152</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>68</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>171695</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>2984257</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>14509692</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>1920705</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>109201</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>38352</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>19733900</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>584</v>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>42775</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>740850</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>6022535</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>999941</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>53533</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>17210</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>7877428</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>2095</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>61041</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>1322609</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>6535961</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>840845</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>37361</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>6269</v>
+      </c>
+      <c r="I10" s="29" t="n">
+        <v>8806181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>54864</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>751861</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>5818639</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>1215186</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>60309</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>20468</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>7921330</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>72</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>117937</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>743282</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>930646</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>367</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>102</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>49</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>1792382</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>11016</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>4248</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>90</v>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>15354</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>3210</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>53386</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>360235</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>51642</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>2608</v>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>1159</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>472253</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>8640</v>
+      </c>
+      <c r="D16" s="29" t="n">
+        <v>143820</v>
+      </c>
+      <c r="E16" s="29" t="n">
+        <v>1172100</v>
+      </c>
+      <c r="F16" s="29" t="n">
+        <v>191280</v>
+      </c>
+      <c r="G16" s="29" t="n">
+        <v>9720</v>
+      </c>
+      <c r="H16" s="29" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <v>1528860</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>11741</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>206248</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>1086862</v>
+      </c>
+      <c r="F17" s="29" t="n">
+        <v>139539</v>
+      </c>
+      <c r="G17" s="29" t="n">
+        <v>6576</v>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>2397</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>1453403</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>313</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>-63369</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>399429</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>-527872</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>-632892</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>-27817</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>-12380</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>-864587</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>КРОНА — Деды Морозы (себес учтён)</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="32" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <v>642</v>
+      </c>
+      <c r="E20" s="34" t="n">
+        <v>6872</v>
+      </c>
+      <c r="F20" s="34" t="n">
+        <v>278</v>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" s="34" t="n">
+        <v>7852</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>Возвраты шт</t>
+        </is>
+      </c>
+      <c r="B21" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <v>55</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="34" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>16436</v>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>643544</v>
+      </c>
+      <c r="E22" s="34" t="n">
+        <v>5992030</v>
+      </c>
+      <c r="F22" s="34" t="n">
+        <v>193682</v>
+      </c>
+      <c r="G22" s="34" t="n">
+        <v>25421</v>
+      </c>
+      <c r="H22" s="34" t="n">
+        <v>9232</v>
+      </c>
+      <c r="I22" s="34" t="n">
+        <v>6880345</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>193118</v>
+      </c>
+      <c r="E23" s="34" t="n">
+        <v>2071722</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>83820</v>
+      </c>
+      <c r="G23" s="34" t="n">
+        <v>9314</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I23" s="34" t="n">
+        <v>2366674</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>5289</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>139773</v>
+      </c>
+      <c r="E24" s="34" t="n">
+        <v>1366473</v>
+      </c>
+      <c r="F24" s="34" t="n">
+        <v>40621</v>
+      </c>
+      <c r="G24" s="34" t="n">
+        <v>-357</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <v>2020</v>
+      </c>
+      <c r="I24" s="34" t="n">
+        <v>1553820</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="34" t="n">
+        <v>4730</v>
+      </c>
+      <c r="D25" s="34" t="n">
+        <v>177094</v>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>2100107</v>
+      </c>
+      <c r="F25" s="34" t="n">
+        <v>120686</v>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>11037</v>
+      </c>
+      <c r="H25" s="34" t="n">
+        <v>4768</v>
+      </c>
+      <c r="I25" s="34" t="n">
+        <v>2418421</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>22</v>
+      </c>
+      <c r="H26" s="34" t="n">
+        <v>59</v>
+      </c>
+      <c r="I26" s="34" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>3467</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>197663</v>
+      </c>
+      <c r="F28" s="34" t="n">
+        <v>3196</v>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="34" t="n">
+        <v>206157</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>275</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>11805</v>
+      </c>
+      <c r="E29" s="34" t="n">
+        <v>133547</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>4663</v>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>483</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <v>290</v>
+      </c>
+      <c r="I29" s="34" t="n">
+        <v>151064</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="34" t="n">
+        <v>900</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <v>38400</v>
+      </c>
+      <c r="E30" s="34" t="n">
+        <v>409020</v>
+      </c>
+      <c r="F30" s="34" t="n">
+        <v>16260</v>
+      </c>
+      <c r="G30" s="34" t="n">
+        <v>1860</v>
+      </c>
+      <c r="H30" s="34" t="n">
+        <v>840</v>
+      </c>
+      <c r="I30" s="34" t="n">
+        <v>467280</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>141</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <v>5168</v>
+      </c>
+      <c r="E31" s="34" t="n">
+        <v>50016</v>
+      </c>
+      <c r="F31" s="34" t="n">
+        <v>8961</v>
+      </c>
+      <c r="G31" s="34" t="n">
+        <v>887</v>
+      </c>
+      <c r="H31" s="34" t="n">
+        <v>438</v>
+      </c>
+      <c r="I31" s="34" t="n">
+        <v>65611</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>2697</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>228061</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>1164521</v>
+      </c>
+      <c r="F32" s="30" t="n">
+        <v>-40570</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>-2526</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <v>-1072</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>1351111</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>ИТОГО 2 МАГАЗИНА — Деды Морозы</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="n"/>
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="36" t="n"/>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="36" t="n"/>
+      <c r="I33" s="36" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>161</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>3065</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>26559</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>3534</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>197</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>33589</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Возвраты шт</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>207</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>188130</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>3627801</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>20501722</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>2114386</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>134622</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>47584</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>26614245</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>584</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>47275</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>933968</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>8094257</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>1083761</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>62847</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>21410</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>10244102</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="n">
+        <v>2095</v>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>66330</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>1462382</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>7902434</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>881466</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>37004</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>8289</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>10360001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>59594</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>928955</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>7918746</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>1335872</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>71346</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>25236</v>
+      </c>
+      <c r="I39" s="8" t="n">
+        <v>10339751</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>131</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>117937</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>743282</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>930646</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>367</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>1792382</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>3467</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>1831</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>208679</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>7444</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>221511</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>3485</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>65191</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>493783</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>56305</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>3091</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1449</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>623316</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>9540</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>182220</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>1581120</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>207540</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>11580</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>4140</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>1996140</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>11882</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>211416</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1136879</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>148500</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>7463</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>2835</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>1519014</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>313</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>-60672</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>627490</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>636650</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>-673461</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>-30343</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>-13453</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>486524</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>ИТОГ СЕЗОНА: продано 33,589 шт | логистика 10,339,751 ₽ | реклама 1,792,382 ₽ | ЧИСТАЯ МАРЖА 486,524 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>Заработали на пике (ноя+дек): 1,264,140 ₽.  Отъели после НГ (янв+фев+мар): -717,257 ₽.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Главный съедатель — ЛОГИСТИКА (ДМ объёмные, ~300-370 ₽/шт). Хранение почти 0 (свой склад FBS). Вывод: продавать в декабре, не тянуть на январь, локализовать склады.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1285,7 +2692,6 @@
         <v>-717257</v>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
@@ -1305,7 +2711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1777,7 +3183,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2067,513 +3473,6 @@
         <is>
           <t>Следствие для плана: не рассчитывать на 350 ₽/шт прибыли. Снижать логистику (локализация складов), минимизировать возвраты, точнее цена под сезон.</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Коротич — по месяцам</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Месяц</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Продажи шт</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Выручка к нам ₽</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>Себестоимость ₽</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>Логистика ₽</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>Хранение ₽</t>
-        </is>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>Реклама ₽</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>Комиссия ₽</t>
-        </is>
-      </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>Платн.приёмка ₽</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>Штрафы ₽</t>
-        </is>
-      </c>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>Брак ₽</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
-        <is>
-          <t>Эквайринг ₽</t>
-        </is>
-      </c>
-      <c r="M3" s="10" t="inlineStr">
-        <is>
-          <t>Прочие ₽</t>
-        </is>
-      </c>
-      <c r="N3" s="10" t="inlineStr">
-        <is>
-          <t>Налог ₽</t>
-        </is>
-      </c>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>Маржа ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Сен 25</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>821</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>57916</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>4350</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>7748</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>21301</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>6100</v>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v>48800</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Окт 25</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>17837</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>15013762</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>6873386</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1614433</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>1364616</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>5913760</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>2448</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>341452</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>1069860</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>1159062</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>2929039</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Ноя 25</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>26288</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>20610927</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>9599475</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>2583792</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>2940391</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>9955699</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>4794</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>462502</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>1575360</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>1532296</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>2377102</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Дек 25</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>48231</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>36563533</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>16818074</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>8226895</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>3575408</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>17618748</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>1158775</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>887696</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>2884140</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>2815863</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>1072372</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Янв 26</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>31623</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>22035559</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>11462986</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>3820235</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>20458</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>2048323</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>10660518</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>498166</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>605191</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>1891500</v>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>1733920</v>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v>558040</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Фев 26</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>27254</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>20601226</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>10554897</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>2330318</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>147495</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>2656259</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>10031358</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>410</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>641987</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>1634280</v>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>1574627</v>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v>1696258</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Мар 26</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>30638</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>28731523</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>14806729</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2934831</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>187104</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>1911573</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>13311854</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>11045</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>1017232</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>1837560</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>2138159</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>4908356</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>182692</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>143556530</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>70173464</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>21510591</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>359407</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>14504317</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>67513238</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>1675637</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>3956659</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>10892700</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>10960027</v>
-      </c>
-      <c r="O11" s="8" t="n">
-        <v>13589968</v>
       </c>
     </row>
   </sheetData>
@@ -2610,7 +3509,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Крона — по месяцам</t>
+          <t>Коротич — по месяцам</t>
         </is>
       </c>
     </row>
@@ -2698,25 +3597,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0</v>
+        <v>57916</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>4350</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0</v>
+        <v>7748</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>21301</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -2728,16 +3627,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0</v>
+        <v>48800</v>
       </c>
     </row>
     <row r="5">
@@ -2747,46 +3646,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>15</v>
+        <v>17837</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16436</v>
+        <v>15013762</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>6873386</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4730</v>
+        <v>1614433</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>1364616</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>5289</v>
+        <v>5913760</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3467</v>
+        <v>2448</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>275</v>
+        <v>341452</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>900</v>
+        <v>1069860</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>141</v>
+        <v>1159062</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>7197</v>
+        <v>2929039</v>
       </c>
     </row>
     <row r="6">
@@ -2796,46 +3695,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>642</v>
+        <v>26288</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>643544</v>
+        <v>20610927</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>9599475</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>177094</v>
+        <v>2583792</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>2940391</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>139773</v>
+        <v>9955699</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1831</v>
+        <v>4794</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>11805</v>
+        <v>462502</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>38400</v>
+        <v>1575360</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>5168</v>
+        <v>1532296</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>421179</v>
+        <v>2377102</v>
       </c>
     </row>
     <row r="7">
@@ -2845,46 +3744,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6886</v>
+        <v>48231</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>6002296</v>
+        <v>36563533</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>16818074</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2101307</v>
+        <v>8226895</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2592</v>
+        <v>3575408</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1369174</v>
+        <v>17618748</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>197663</v>
+        <v>1158775</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>133756</v>
+        <v>887696</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>409860</v>
+        <v>2884140</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>50109</v>
+        <v>2815863</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>3241785</v>
+        <v>1072372</v>
       </c>
     </row>
     <row r="8">
@@ -2894,46 +3793,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>350</v>
+        <v>31623</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>244080</v>
+        <v>22035559</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>11462986</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>127982</v>
+        <v>3820235</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>6</v>
+        <v>20458</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>426</v>
+        <v>2048323</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>53912</v>
+        <v>10660518</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>3196</v>
+        <v>498166</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5808</v>
+        <v>605191</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>20580</v>
+        <v>1891500</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>11547</v>
+        <v>1733920</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>79019</v>
+        <v>558040</v>
       </c>
     </row>
     <row r="9">
@@ -2943,46 +3842,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>205</v>
+        <v>27254</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>151471</v>
+        <v>20601226</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>10554897</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>29260</v>
+        <v>2330318</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>184</v>
+        <v>147495</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1</v>
+        <v>2656259</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>33030</v>
+        <v>10031358</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3912</v>
+        <v>641987</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>12300</v>
+        <v>1634280</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>7228</v>
+        <v>1574627</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>97705</v>
+        <v>1696258</v>
       </c>
     </row>
     <row r="10">
@@ -2992,46 +3891,46 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>66</v>
+        <v>30638</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>58271</v>
+        <v>28731523</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>14806729</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>10951</v>
+        <v>2934831</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>361</v>
+        <v>187104</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>1911573</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>15073</v>
+        <v>13311854</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0</v>
+        <v>11045</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1873</v>
+        <v>1017232</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3960</v>
+        <v>1837560</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2749</v>
+        <v>2138159</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>40971</v>
+        <v>4908356</v>
       </c>
     </row>
     <row r="11">
@@ -3041,46 +3940,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>8164</v>
+        <v>182692</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>7116097</v>
+        <v>143556530</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>0</v>
+        <v>70173464</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>2451322</v>
+        <v>21510591</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>551</v>
+        <v>359407</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>3018</v>
+        <v>14504317</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1616252</v>
+        <v>67513238</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>206157</v>
+        <v>1675637</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>157430</v>
+        <v>3956659</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>486000</v>
+        <v>10892700</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>76942</v>
+        <v>10960027</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>3887857</v>
+        <v>13589968</v>
       </c>
     </row>
   </sheetData>
@@ -3115,9 +4014,9 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>Коротич ДМ — по месяцам</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Крона — по месяцам</t>
         </is>
       </c>
     </row>
@@ -3205,25 +4104,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0</v>
@@ -3235,16 +4134,16 @@
         <v>0</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3254,46 +4153,46 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>171695</v>
+        <v>16436</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>42775</v>
+        <v>0</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54864</v>
+        <v>4730</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>117937</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>61041</v>
+        <v>5289</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>3467</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3210</v>
+        <v>275</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>8640</v>
+        <v>900</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>11741</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>-63369</v>
+        <v>141</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>7197</v>
       </c>
     </row>
     <row r="6">
@@ -3303,46 +4202,46 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2423</v>
+        <v>642</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2984257</v>
+        <v>643544</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>740850</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>751861</v>
+        <v>177094</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>743282</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1322609</v>
+        <v>139773</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>1831</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53386</v>
+        <v>11805</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>143820</v>
+        <v>38400</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>206248</v>
+        <v>5168</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>399429</v>
+        <v>421179</v>
       </c>
     </row>
     <row r="7">
@@ -3352,46 +4251,46 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>19687</v>
+        <v>6886</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>14509692</v>
+        <v>6002296</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6022535</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5818639</v>
+        <v>2101307</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>930646</v>
+        <v>2592</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>6535961</v>
+        <v>1369174</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>11016</v>
+        <v>197663</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>360235</v>
+        <v>133756</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1172100</v>
+        <v>409860</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>1086862</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>-527872</v>
+        <v>50109</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>3241785</v>
       </c>
     </row>
     <row r="8">
@@ -3401,46 +4300,46 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3256</v>
+        <v>350</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1920705</v>
+        <v>244080</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>999941</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1215186</v>
+        <v>127982</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>367</v>
+        <v>426</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>840845</v>
+        <v>53912</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>4248</v>
+        <v>3196</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>51642</v>
+        <v>5808</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>191280</v>
+        <v>20580</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>139539</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>-632892</v>
+        <v>11547</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>79019</v>
       </c>
     </row>
     <row r="9">
@@ -3450,46 +4349,46 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>109201</v>
+        <v>151471</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>53533</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>60309</v>
+        <v>29260</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>37361</v>
+        <v>33030</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2608</v>
+        <v>3912</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>9720</v>
+        <v>12300</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>6576</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>-27817</v>
+        <v>7228</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>97705</v>
       </c>
     </row>
     <row r="10">
@@ -3499,25 +4398,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>38352</v>
+        <v>58271</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>17210</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>20468</v>
+        <v>10951</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>72</v>
+        <v>361</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6269</v>
+        <v>15073</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>0</v>
@@ -3529,16 +4428,16 @@
         <v>0</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1159</v>
+        <v>1873</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>2397</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>-12380</v>
+        <v>2749</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>40971</v>
       </c>
     </row>
     <row r="11">
@@ -3548,46 +4447,46 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>25737</v>
+        <v>8164</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>19733900</v>
+        <v>7116097</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>7877428</v>
+        <v>0</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>7921330</v>
+        <v>2451322</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>259</v>
+        <v>551</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>1792382</v>
+        <v>3018</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>8806181</v>
+        <v>1616252</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>15354</v>
+        <v>206157</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>472253</v>
+        <v>157430</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>1528860</v>
+        <v>486000</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>1453403</v>
+        <v>76942</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>-864587</v>
+        <v>3887857</v>
       </c>
     </row>
   </sheetData>
@@ -3624,6 +4523,513 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
+          <t>Коротич ДМ — по месяцам</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Месяц</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Продажи шт</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Выручка к нам ₽</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость ₽</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Логистика ₽</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Хранение ₽</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Реклама ₽</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Комиссия ₽</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Платн.приёмка ₽</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>Штрафы ₽</t>
+        </is>
+      </c>
+      <c r="K3" s="10" t="inlineStr">
+        <is>
+          <t>Брак ₽</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Эквайринг ₽</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
+        <is>
+          <t>Прочие ₽</t>
+        </is>
+      </c>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>Налог ₽</t>
+        </is>
+      </c>
+      <c r="O3" s="10" t="inlineStr">
+        <is>
+          <t>Маржа ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Сен 25</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>584</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2095</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Окт 25</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>171695</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>42775</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>54864</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>117937</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>61041</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>3210</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>8640</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>11741</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>-63369</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ноя 25</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2423</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2984257</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>740850</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>751861</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>743282</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1322609</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>53386</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>143820</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>206248</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>399429</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Дек 25</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>19687</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>14509692</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6022535</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5818639</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>930646</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>6535961</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>11016</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>360235</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1172100</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1086862</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>-527872</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Янв 26</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3256</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1920705</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>999941</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1215186</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>367</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>840845</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>4248</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>51642</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>191280</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>139539</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>-632892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Фев 26</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>109201</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>53533</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>60309</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>37361</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2608</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>9720</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>6576</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>-27817</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Мар 26</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>38352</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>17210</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>20468</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6269</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1159</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2397</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>-12380</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>25737</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>19733900</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>7877428</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>7921330</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>259</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>1792382</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>8806181</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>15354</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>472253</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>1528860</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>1453403</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>-864587</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
           <t>Крона ДМ — по месяцам</t>
         </is>
       </c>
